--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -2843,7 +2843,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3154,7 +3154,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>8002440.731534923</v>
+        <v>8003550.333979755</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="15">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-5044713.442541719</v>
+        <v>-5044716.385903903</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>8342620.978314899</v>
+        <v>8343733.524121915</v>
       </c>
     </row>
     <row r="18">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3297907.53577318</v>
+        <v>-3299017.138218012</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>74989.83825372369</v>
+        <v>73880.23580889196</v>
       </c>
     </row>
     <row r="23">
@@ -656,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-03T15:21:25+00:00</t>
+          <t>2026-08-03T23:48:56+00:00</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>888981.8667311786</v>
+        <v>888359.3384817669</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>888981.8667311786</v>
+        <v>888359.3384817669</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>14451.90719582068</v>
+        <v>15074.43544523234</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>649205.5920411288</v>
+        <v>648750.9721710883</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>649205.5920411288</v>
+        <v>648750.9721710883</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>42510.12856612542</v>
+        <v>42964.74843616584</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1121,13 +1121,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>443804.6873183274</v>
+        <v>443493.9037518494</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>443804.6873183274</v>
+        <v>443493.9037518494</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>7214.79750512636</v>
+        <v>7525.581071604342</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1186,13 +1186,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>349190.1231148468</v>
+        <v>348945.5953869035</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>349190.1231148468</v>
+        <v>348945.5953869035</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>191752.4768851532</v>
+        <v>191997.0046130965</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>228095.397829291</v>
+        <v>227935.6692296159</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>228095.397829291</v>
+        <v>227935.6692296159</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-110133.5967546589</v>
+        <v>-109973.8681549838</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>210760.3820548953</v>
+        <v>210612.7926646095</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>210760.3820548953</v>
+        <v>210612.7926646095</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>51969.65447224214</v>
+        <v>52117.24386252792</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1381,13 +1381,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>112016.300540162</v>
+        <v>111937.8587697609</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>112016.300540162</v>
+        <v>111937.8587697609</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-112016.300540162</v>
+        <v>-111937.8587697609</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1446,13 +1446,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>94386.77076623733</v>
+        <v>94320.67444484802</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>94386.77076623733</v>
+        <v>94320.67444484802</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>173431.9392337627</v>
+        <v>173498.035555152</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>85968.60540771921</v>
+        <v>85908.40408367464</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>85968.60540771921</v>
+        <v>85908.40408367464</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-14556.5356027653</v>
+        <v>-14496.33427872073</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>85706.38674064209</v>
+        <v>85646.36904073418</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>85706.38674064209</v>
+        <v>85646.36904073418</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78365.1121326421</v>
+        <v>-78305.09443273417</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1641,13 +1641,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85541.7698691449</v>
+        <v>85481.86744566351</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>85541.7698691449</v>
+        <v>85481.86744566351</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-85385.52115947533</v>
+        <v>-85325.61873599394</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>58082.52132816915</v>
+        <v>58041.84782100662</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>58082.52132816915</v>
+        <v>58041.84782100662</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-2847.090682996822</v>
+        <v>-2806.417175834302</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1771,13 +1771,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3422.786112775443</v>
+        <v>3420.389234811294</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3422.786112775443</v>
+        <v>3420.389234811294</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-292.5635991577442</v>
+        <v>-290.1667211935945</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1790,12 +1790,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>999999</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -1830,19 +1830,19 @@
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>654384.2290322618</v>
+        <v>1000000</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>2238.928187303652</v>
+        <v>3419.031558965996</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2238.928187303652</v>
+        <v>3419.031558965996</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-2238.928187303652</v>
+        <v>-3419.031558965996</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1855,12 +1855,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7547666.106224</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-7547666.106224</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1895,19 +1895,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>137651.9570648836</v>
+        <v>654384.2290322618</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>470.9661893378022</v>
+        <v>2237.360330750935</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>470.9661893378022</v>
+        <v>2237.360330750935</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-470.9661893378022</v>
+        <v>-2237.360330750935</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1920,12 +1920,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>7547666.106224</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>-7547666.106224</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -1960,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>137651.9570648836</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>34.45028097485242</v>
+        <v>470.6363853582693</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>34.45028097485242</v>
+        <v>470.6363853582693</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-34.45028097485242</v>
+        <v>-470.6363853582693</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1985,12 +1985,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2000,44 +2000,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>10068.978846</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>10068.978846</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001261042598236517</v>
+        <v>34.42615644103502</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001261042598236517</v>
+        <v>34.42615644103502</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0004750288905756651</v>
+        <v>-34.42615644103502</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2050,12 +2050,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2069,40 +2069,40 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.421427485522837e-09</v>
+        <v>0.001260159526634618</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.421427485522837e-09</v>
+        <v>0.001260159526634618</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.421427485522837e-09</v>
+        <v>-0.0004741458189737658</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2115,12 +2115,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2130,14 +2130,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -2155,19 +2155,19 @@
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>3.419031558965996e-09</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>3.419031558965996e-09</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>-3.419031558965996e-09</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -2245,12 +2245,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -2310,12 +2310,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2435,21 +2435,17 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2459,7 +2455,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -2487,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2504,17 +2500,21 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2574,12 +2574,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2639,17 +2639,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2704,17 +2704,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2765,6 +2765,136 @@
         <v>0</v>
       </c>
       <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2817,7 +2947,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1040015121.219713</v>
+        <v>1040369959.51144</v>
       </c>
     </row>
     <row r="6">
@@ -2827,7 +2957,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>989187917.9278593</v>
+        <v>989284692.443311</v>
       </c>
     </row>
     <row r="7">
@@ -2837,7 +2967,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>50827203.29185378</v>
+        <v>51085267.06812943</v>
       </c>
     </row>
     <row r="8">
@@ -2847,7 +2977,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.03852333586414389</v>
+        <v>0.03852302248128459</v>
       </c>
     </row>
     <row r="9">
@@ -2877,7 +3007,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03804035608798387</v>
+        <v>0.03804017286855644</v>
       </c>
     </row>
     <row r="12">
@@ -2887,7 +3017,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-4.829797761600159</v>
+        <v>-4.828496127281479</v>
       </c>
     </row>
     <row r="13">
@@ -2897,7 +3027,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>41096.77961270168</v>
+        <v>41099.72297488574</v>
       </c>
     </row>
     <row r="15">
@@ -2907,7 +3037,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3339004.315385882</v>
+        <v>3340116.861192898</v>
       </c>
     </row>
     <row r="16">
@@ -2917,7 +3047,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="17">
@@ -2927,7 +3057,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>41096.77961270168</v>
+        <v>41099.72297488574</v>
       </c>
     </row>
     <row r="19">
@@ -2954,10 +3084,10 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>989187917.9278593</v>
+        <v>989284692.443311</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3138450.67521212</v>
+        <v>3138758.209130579</v>
       </c>
     </row>
     <row r="21">
@@ -2967,10 +3097,10 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>50827203.29185378</v>
+        <v>51085267.06812943</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>159456.8605610603</v>
+        <v>160258.9290874331</v>
       </c>
     </row>
     <row r="23">
@@ -2992,7 +3122,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="25">
@@ -3012,7 +3142,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8002440.731534923</v>
+        <v>8003550.333979755</v>
       </c>
     </row>
     <row r="28">
@@ -3029,7 +3159,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8342620.978314899</v>
+        <v>8343733.524121915</v>
       </c>
     </row>
     <row r="31">
@@ -3039,7 +3169,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="32">
@@ -3049,7 +3179,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-5044713.442541719</v>
+        <v>-5044716.385903903</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -3897,7 +4027,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>2561481535.405515</v>
+        <v>2561481536.405415</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -3915,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>993095417.5078532</v>
+        <v>993095418.5077531</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -3933,10 +4063,10 @@
         <v>0.03850200106642065</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102795.5690940567</v>
+        <v>102795.5691975566</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>267635.5478660245</v>
+        <v>267635.5479711227</v>
       </c>
     </row>
     <row r="15">
@@ -3946,7 +4076,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2556482110.405515</v>
+        <v>2556482111.405415</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -3964,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>987923845.7009054</v>
+        <v>987923846.7008054</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -3982,10 +4112,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102651.214615515</v>
+        <v>102651.2147194106</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>267505.8000832992</v>
+        <v>267505.8001883973</v>
       </c>
     </row>
     <row r="16">
@@ -3995,7 +4125,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>2556214289.88574</v>
+        <v>2556214290.88564</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4013,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>987656025.1811304</v>
+        <v>987656026.1810305</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4031,10 +4161,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>102623.3864567217</v>
+        <v>102623.3865606173</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>267477.6498184584</v>
+        <v>267477.6499235565</v>
       </c>
     </row>
     <row r="17">
@@ -4044,7 +4174,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2556214289.88574</v>
+        <v>2556214290.88564</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4062,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>987656025.1811304</v>
+        <v>987656026.1810305</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4080,10 +4210,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>102623.3864567217</v>
+        <v>102623.3865606173</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>267477.6498184584</v>
+        <v>267477.6499235565</v>
       </c>
     </row>
     <row r="18">
@@ -4093,7 +4223,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2562714289.88574</v>
+        <v>2562714290.88564</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4111,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>993726254.3711056</v>
+        <v>993726255.3710055</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4129,10 +4259,10 @@
         <v>0.03895200106642065</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>104040.4548117799</v>
+        <v>104040.4549164667</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>268952.1558600348</v>
+        <v>268952.155965133</v>
       </c>
     </row>
     <row r="19">
@@ -4142,7 +4272,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>2564714188.849935</v>
+        <v>2564714189.849835</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4160,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>995613022.3902465</v>
+        <v>995613023.3901465</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4178,10 +4308,10 @@
         <v>0.03857700106642065</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>103253.1737163269</v>
+        <v>103253.1738200246</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>268173.2025927747</v>
+        <v>268173.2026978729</v>
       </c>
     </row>
     <row r="20">
@@ -4191,7 +4321,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>2570714188.849935</v>
+        <v>2570714189.849835</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4209,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1001442087.296572</v>
+        <v>1001442088.296472</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4227,10 +4357,10 @@
         <v>0.03850200106642065</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>103661.8401635675</v>
+        <v>103661.8402686657</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>268605.980004166</v>
+        <v>268605.9801092641</v>
       </c>
     </row>
     <row r="21">
@@ -4240,7 +4370,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>2570714188.849935</v>
+        <v>2570714189.849835</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4258,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1001292411.660789</v>
+        <v>1001292412.660689</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4276,10 +4406,10 @@
         <v>0.03857700106642065</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>103843.9827007875</v>
+        <v>103843.9828058857</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>268803.8547518642</v>
+        <v>268803.8548569624</v>
       </c>
     </row>
     <row r="22">
@@ -4289,7 +4419,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>2570714544.573842</v>
+        <v>2570714545.573742</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4307,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1001145523.947395</v>
+        <v>1001145524.947296</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4325,10 +4455,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>104026.4040231741</v>
+        <v>104026.4041282723</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>269001.752639525</v>
+        <v>269001.7527446232</v>
       </c>
     </row>
     <row r="23">
@@ -4338,7 +4468,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2570714544.573842</v>
+        <v>2570714545.573742</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4356,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1001145523.947395</v>
+        <v>1001145524.947296</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4374,10 +4504,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>104026.4040231741</v>
+        <v>104026.4041282723</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>269001.752639525</v>
+        <v>269001.7527446232</v>
       </c>
     </row>
     <row r="24">
@@ -4387,7 +4517,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>2570714544.573842</v>
+        <v>2570714545.573742</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4405,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>1001145523.947395</v>
+        <v>1001145524.947296</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4423,10 +4553,10 @@
         <v>0.03865200106642065</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>104026.4040231741</v>
+        <v>104026.4041282723</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>269001.752639525</v>
+        <v>269001.7527446232</v>
       </c>
     </row>
     <row r="25">
@@ -4436,7 +4566,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>2482128027.103577</v>
+        <v>2482128028.103477</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4454,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>912114860.623396</v>
+        <v>912114861.623296</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4472,10 +4602,10 @@
         <v>0.03872700106642065</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>94954.66475509458</v>
+        <v>94954.66485918801</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>259888.3858049891</v>
+        <v>259888.3859100873</v>
       </c>
     </row>
     <row r="26">
@@ -4485,7 +4615,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2455799609.582397</v>
+        <v>2456799610.582297</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4503,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>885641580.9107099</v>
+        <v>886641581.9106098</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4521,10 +4651,10 @@
         <v>0.03880200106642065</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>92373.90277689909</v>
+        <v>92478.20455894344</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>257318.8722505766</v>
+        <v>257423.9810488564</v>
       </c>
     </row>
     <row r="27">
@@ -4534,7 +4664,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2503299609.582397</v>
+        <v>2504299610.572297</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4552,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>933009388.0383854</v>
+        <v>934009389.0282854</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.03600000425292382</v>
@@ -4570,10 +4700,10 @@
         <v>0.03895200106642065</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>97683.56290093865</v>
+        <v>97788.26030361245</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>262707.1564575486</v>
+        <v>262812.2652547772</v>
       </c>
     </row>
     <row r="28">
@@ -4583,7 +4713,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2558799834.914424</v>
+        <v>2559799835.904324</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4601,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>988389035.8587762</v>
+        <v>989389036.8486762</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4619,10 +4749,10 @@
         <v>0.03661759962619772</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>97389.83485859133</v>
+        <v>97488.36886466737</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>254817.3876794045</v>
+        <v>254917.6466288517</v>
       </c>
     </row>
     <row r="29">
@@ -4632,7 +4762,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2606299834.914424</v>
+        <v>2607299835.904324</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4650,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>1035802153.989139</v>
+        <v>1036802154.979039</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4668,10 +4798,10 @@
         <v>0.03661759962619772</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>102123.3913309844</v>
+        <v>102223.6502804317</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>259579.6830639539</v>
+        <v>259679.9420134012</v>
       </c>
     </row>
     <row r="30">
@@ -4681,7 +4811,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2657799834.914424</v>
+        <v>2658799835.904324</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4699,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1087302153.989139</v>
+        <v>1088302154.979039</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4717,10 +4847,10 @@
         <v>0.03661759962619772</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>107286.722116338</v>
+        <v>107386.9810657853</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>264743.0138493075</v>
+        <v>264843.2727987547</v>
       </c>
     </row>
     <row r="31">
@@ -4730,7 +4860,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2713299834.914424</v>
+        <v>2714299835.904324</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4748,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>1142802153.989139</v>
+        <v>1143802154.979039</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4766,10 +4896,10 @@
         <v>0.03661759962619772</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>112851.0883024957</v>
+        <v>112951.347251943</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>270307.3800354652</v>
+        <v>270407.6389849125</v>
       </c>
     </row>
     <row r="32">
@@ -4779,7 +4909,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2732299834.914424</v>
+        <v>2733299835.904324</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4797,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1161347213.689556</v>
+        <v>1162347214.679456</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4815,10 +4945,10 @@
         <v>0.03661759962619772</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>114710.3946649692</v>
+        <v>114810.6536144164</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>272212.298189285</v>
+        <v>272312.5571387323</v>
       </c>
     </row>
     <row r="33">
@@ -4828,7 +4958,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2751299834.914424</v>
+        <v>2752299835.904324</v>
       </c>
       <c r="C33" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4846,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1180202653.755229</v>
+        <v>1181202654.745129</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4864,10 +4994,10 @@
         <v>0.03669259962619772</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>116799.052858308</v>
+        <v>116899.3118077553</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>274315.4497954246</v>
+        <v>274415.7087448719</v>
       </c>
     </row>
     <row r="34">
@@ -4877,7 +5007,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2792199834.914424</v>
+        <v>2793199823.952939</v>
       </c>
       <c r="C34" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4895,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1220905611.040843</v>
+        <v>1221905600.079358</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4913,10 +5043,10 @@
         <v>0.03669259962619772</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>120879.8845555458</v>
+        <v>120980.1423067609</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>278416.0367686471</v>
+        <v>278516.2945198623</v>
       </c>
     </row>
     <row r="35">
@@ -4926,7 +5056,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>2792199834.914424</v>
+        <v>2793199823.952939</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4944,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1220654348.29117</v>
+        <v>1221654337.329685</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -4962,10 +5092,10 @@
         <v>0.03669259962619772</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>120854.6932411652</v>
+        <v>120954.9509923804</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>278416.0367686471</v>
+        <v>278516.2945198623</v>
       </c>
     </row>
     <row r="36">
@@ -4975,7 +5105,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>2792199834.914424</v>
+        <v>2793199823.952939</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>2.980232238769531e-08</v>
@@ -4993,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1220498592.905816</v>
+        <v>1221498581.944331</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.03519999850777533</v>
@@ -5011,10 +5141,10 @@
         <v>0.03676759962619772</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>121037.2965359658</v>
+        <v>121137.554287181</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>278614.255919296</v>
+        <v>278714.5136705112</v>
       </c>
     </row>
     <row r="38">
@@ -5036,10 +5166,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3297907.53577318</v>
+        <v>3299017.138218012</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>8342620.978314899</v>
+        <v>8343733.524121915</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,168 +505,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>3444921.14564746</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>28898.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>3473819.385647459</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>4704533.195761743</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>8003550.333979755</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-5044716.385903903</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>8343733.524121915</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>3372897.374026904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3372897.374026904</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-3299017.138218012</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>73880.23580889196</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-07-01 → 2026-07-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
+          <t>2026-07-01 → 2026-07-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-03T23:48:56+00:00</t>
+          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:48:56+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -515,168 +515,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>3473819.385647459</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13214.77557626936</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>3487034.161223729</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>4704533.195761743</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>8003550.333979755</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-5044716.385903903</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>8343733.524121915</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>3372897.374026904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3372897.374026904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-3299017.138218012</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
         <v>73880.23580889196</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-07-01 → 2026-07-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
+          <t>2026-07-01 → 2026-07-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-03T23:48:56+00:00</t>
+          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:04:20+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>13214.77557626936</v>
+        <v>13102.07817737222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>3487034.161223729</v>
+        <v>3486921.463824832</v>
       </c>
     </row>
     <row r="10">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-04T23:04:20+00:00</t>
+          <t>2026-08-04T23:14:13+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -515,168 +515,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>3473819.385647459</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>13102.07817737222</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>3486921.463824832</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>4704533.195761743</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>8003550.333979755</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3299017.138218012</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3299017.138218012</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-5044716.385903903</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>8343733.524121915</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>3372897.374026904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3372897.374026904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-3299017.138218012</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
         <v>73880.23580889196</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-07-01 → 2026-07-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
+          <t>2026-07-01 → 2026-07-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-03T23:48:56+00:00</t>
+          <t>avalanche_c=91716609, base=49376526, ethereum=25656292, monad=92053501, plume=84574746</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:14:13+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3372897.374026904</v>
+        <v>4841078.809624951</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>3486921.463824832</v>
+        <v>4955102.899422878</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3372897.374026904</v>
+        <v>4841078.809624951</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>73880.23580889196</v>
+        <v>1542061.671406939</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-04T23:14:13+00:00</t>
+          <t>2026-08-05T21:40:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1256,10 +1256,10 @@
         <v>117961.8010746321</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>1468181.435598047</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>117961.8010746321</v>
+        <v>1586143.236672679</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>227935.6692296159</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-109973.8681549838</v>
+        <v>1358207.567443063</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-05T21:40:01+00:00</t>
+          <t>2026-08-05T22:21:57+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3372897.374026904</v>
+        <v>4841078.809624951</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>3486921.463824832</v>
+        <v>4955102.899422878</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3372897.374026904</v>
+        <v>4841078.809624951</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>73880.23580889196</v>
+        <v>1542061.671406939</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-04T23:14:13+00:00</t>
+          <t>2026-08-05T22:21:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1256,10 +1256,10 @@
         <v>117961.8010746321</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>1468181.435598047</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>117961.8010746321</v>
+        <v>1586143.236672679</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>227935.6692296159</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-109973.8681549838</v>
+        <v>1358207.567443063</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4841078.809624951</v>
+        <v>4862776.031774594</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>4955102.899422878</v>
+        <v>4976800.121572522</v>
       </c>
     </row>
     <row r="10">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4841078.809624951</v>
+        <v>4862776.031774594</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1542061.671406939</v>
+        <v>1563758.893556583</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-05T22:21:57+00:00</t>
+          <t>2026-08-06T00:23:10+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>888359.3384817669</v>
+        <v>888274.3538063347</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>888359.3384817669</v>
+        <v>888274.3538063347</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>15074.43544523234</v>
+        <v>15159.42012066455</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>648750.9721710883</v>
+        <v>648688.9095704964</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>648750.9721710883</v>
+        <v>648688.9095704964</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>42964.74843616584</v>
+        <v>43026.81103675776</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>443493.9037518494</v>
+        <v>443451.4770177184</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>443493.9037518494</v>
+        <v>443451.4770177184</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>7525.581071604342</v>
+        <v>7568.007805735296</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>348945.5953869035</v>
+        <v>348912.2135932049</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>348945.5953869035</v>
+        <v>348912.2135932049</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>191997.0046130965</v>
+        <v>192030.3864067951</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>227935.6692296159</v>
+        <v>227913.8638204422</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>227935.6692296159</v>
+        <v>227913.8638204422</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1358207.567443063</v>
+        <v>1358229.372852237</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>210612.7926646095</v>
+        <v>210592.6444441191</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>210612.7926646095</v>
+        <v>210592.6444441191</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>52117.24386252792</v>
+        <v>52137.39208301836</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1374,40 +1374,40 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32831954.51210045</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32853651.7342501</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32831954.51210045</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>111937.8587697609</v>
+        <v>112242.7499173044</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>111937.8587697609</v>
+        <v>112242.7499173044</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-111937.8587697609</v>
+        <v>-90545.52776766065</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>94320.67444484802</v>
+        <v>94311.65128095812</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>94320.67444484802</v>
+        <v>94311.65128095812</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>173498.035555152</v>
+        <v>173507.0587190419</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>85908.40408367464</v>
+        <v>85900.18567753909</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>85908.40408367464</v>
+        <v>85900.18567753909</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-14496.33427872073</v>
+        <v>-14488.11587258519</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>85646.36904073418</v>
+        <v>85638.17570211591</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>85646.36904073418</v>
+        <v>85638.17570211591</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78305.09443273417</v>
+        <v>-78296.90109411592</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85481.86744566351</v>
+        <v>85473.68984404948</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>85481.86744566351</v>
+        <v>85473.68984404948</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-85325.61873599394</v>
+        <v>-85317.4411343799</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>58041.84782100662</v>
+        <v>58036.29526205341</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>58041.84782100662</v>
+        <v>58036.29526205341</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-2806.417175834302</v>
+        <v>-2800.864616881092</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3420.389234811294</v>
+        <v>3420.062024124828</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3420.389234811294</v>
+        <v>3420.062024124828</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-290.1667211935945</v>
+        <v>-289.8395105071294</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1856,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3419.031558965996</v>
+        <v>3418.704478161254</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3419.031558965996</v>
+        <v>3418.704478161254</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-3419.031558965996</v>
+        <v>-3418.704478161254</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2237.360330750935</v>
+        <v>2237.146294230693</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2237.360330750935</v>
+        <v>2237.146294230693</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-2237.360330750935</v>
+        <v>-2237.146294230693</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>470.6363853582693</v>
+        <v>470.591362045378</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>470.6363853582693</v>
+        <v>470.591362045378</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-470.6363853582693</v>
+        <v>-470.591362045378</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>34.42615644103502</v>
+        <v>34.42286307133113</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>34.42615644103502</v>
+        <v>34.42286307133113</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-34.42615644103502</v>
+        <v>-34.42286307133113</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.001260159526634618</v>
+        <v>0.001260038973786547</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.001260159526634618</v>
+        <v>0.001260038973786547</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-0.0004741458189737658</v>
+        <v>-0.0004740252661256955</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3.419031558965996e-09</v>
+        <v>3.418704478161253e-09</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3.419031558965996e-09</v>
+        <v>3.418704478161253e-09</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>-3.419031558965996e-09</v>
+        <v>-3.418704478161253e-09</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
+++ b/settlements/grove/2026-07/grove_settlement_july_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4862776.031774594</v>
+        <v>4862776.281774594</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>72023.77162055549</v>
+        <v>72123.83220433119</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>13102.07817737222</v>
+        <v>12956.21134119682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>4976800.121572522</v>
+        <v>4976754.565320123</v>
       </c>
     </row>
     <row r="10">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
     </row>
     <row r="12">
@@ -565,7 +565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" s="4" t="n">
-        <v>8003550.333979755</v>
+        <v>8043489.589661337</v>
       </c>
     </row>
     <row r="15">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
     </row>
     <row r="17">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-5044716.385903903</v>
+        <v>-5052104.963353925</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" s="4" t="n">
-        <v>8343733.524121915</v>
+        <v>8391061.35725352</v>
       </c>
     </row>
     <row r="20">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4862776.031774594</v>
+        <v>4862776.281774594</v>
       </c>
     </row>
     <row r="22">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3299017.138218012</v>
+        <v>-3338956.393899593</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1563758.893556583</v>
+        <v>1523819.887875001</v>
       </c>
     </row>
     <row r="25">
@@ -676,7 +676,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-06T00:23:10+00:00</t>
+          <t>2026-09-02T03:04:00+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1011,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>888274.3538063347</v>
+        <v>829242.4866249897</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>888274.3538063347</v>
+        <v>829242.4866249897</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>15159.42012066455</v>
+        <v>74191.28730200963</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1076,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>648688.9095704964</v>
+        <v>605579.1232891669</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>648688.9095704964</v>
+        <v>605579.1232891669</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>43026.81103675776</v>
+        <v>86136.59731808721</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>443451.4770177184</v>
+        <v>413981.1128441867</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>443451.4770177184</v>
+        <v>413981.1128441867</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>7568.007805735296</v>
+        <v>37038.37197926702</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1206,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>348912.2135932049</v>
+        <v>325724.6259267103</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>348912.2135932049</v>
+        <v>325724.6259267103</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>192030.3864067951</v>
+        <v>215217.9740732897</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1225,12 +1225,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA RLUSD (aToken)</t>
+          <t>Galaxy Warehouse (off-chain facility — cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1240,44 +1240,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>171742374.6295398</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.01425431258186553</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-171742374.6152855</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>117961.8010746321</v>
+        <v>0.25</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1468181.435598047</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1586143.236672679</v>
+        <v>0.25</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>66666734.51196501</v>
+        <v>81209677.77419356</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>227913.8638204422</v>
+        <v>259181.3633679711</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>227913.8638204422</v>
+        <v>259181.3633679711</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1358229.372852237</v>
+        <v>-259181.1133679711</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1285,17 +1285,21 @@
       <c r="R8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>(off-chain notional)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Aave Horizon RWA RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1305,44 +1309,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>100671412.0073843</v>
+        <v>171742374.6295398</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>0.01425431258186553</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-100671412.0073843</v>
+        <v>-171742374.6152855</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>262730.0365271374</v>
+        <v>117961.8010746321</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>1468181.435598047</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>262730.0365271374</v>
+        <v>1586143.236672679</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>61600131.21619278</v>
+        <v>66666734.51196501</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>210592.6444441191</v>
+        <v>212767.4387546017</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>210592.6444441191</v>
+        <v>212767.4387546017</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>52137.39208301836</v>
+        <v>1373375.797918078</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1355,59 +1359,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>plume</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>32831954.51210045</v>
+        <v>100671412.0073843</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>32853651.7342501</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>21697.22214964375</v>
+        <v>-100671412.0073843</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>21697.22214964375</v>
+        <v>262730.0365271374</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>21697.22214964375</v>
+        <v>262730.0365271374</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>32831954.51210045</v>
+        <v>61600131.21619278</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>112242.7499173044</v>
+        <v>196597.3321141811</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>112242.7499173044</v>
+        <v>196597.3321141811</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-90545.52776766065</v>
+        <v>66132.70441295631</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1420,17 +1424,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galaxy Arch CLO Token (GACLO-1)</t>
+          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>plume</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1439,40 +1443,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>27586956.37</v>
+        <v>32831954.51210045</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27586956.37</v>
+        <v>32853651.7342501</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>267818.71</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>267818.71</v>
+        <v>21697.22214964375</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>27586956.37</v>
+        <v>32831954.51210045</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>94311.65128095812</v>
+        <v>104783.4564267351</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>94311.65128095812</v>
+        <v>104783.4564267351</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>173507.0587190419</v>
+        <v>-83086.23427709134</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1485,59 +1489,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
+          <t>Galaxy Arch CLO Token (GACLO-1)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>25126531.47596437</v>
+        <v>27586956.37</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>25197943.54576933</v>
+        <v>27586956.37</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>71412.06980495391</v>
+        <v>0</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>71412.06980495391</v>
+        <v>267818.71</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>71412.06980495391</v>
+        <v>267818.71</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25126531.47596437</v>
+        <v>27586956.37</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>85900.18567753909</v>
+        <v>88044.00114762479</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>85900.18567753909</v>
+        <v>88044.00114762479</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-14488.11587258519</v>
+        <v>179774.7088523752</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1550,12 +1554,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
+          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1565,44 +1569,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>25049891.340177</v>
+        <v>25126531.47596437</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>25057232.614785</v>
+        <v>25197943.54576933</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>7341.274608</v>
+        <v>71412.06980495391</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>7341.274608</v>
+        <v>71412.06980495391</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>7341.274608</v>
+        <v>71412.06980495391</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>25049891.340177</v>
+        <v>25126531.47596437</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>85638.17570211591</v>
+        <v>80191.53459463849</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>85638.17570211591</v>
+        <v>80191.53459463849</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78296.90109411592</v>
+        <v>-8779.46478968458</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1615,12 +1619,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Curve AUSD/USDC stableswap LP</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1634,40 +1638,40 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>25001777.83428108</v>
+        <v>25049891.340177</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>25001934.08299074</v>
+        <v>25057232.614785</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>156.2487096695697</v>
+        <v>7341.274608</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>156.2487096695697</v>
+        <v>7341.274608</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>156.2487096695697</v>
+        <v>7341.274608</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25001777.83428108</v>
+        <v>25049891.340177</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85473.68984404948</v>
+        <v>79946.93696260122</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>85473.68984404948</v>
+        <v>79946.93696260122</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-85317.4411343799</v>
+        <v>-72605.66235460121</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1680,59 +1684,59 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>Curve AUSD/USDC stableswap LP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>6027300.885906675</v>
+        <v>25001777.83428108</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>74985592.29829088</v>
+        <v>25001934.08299074</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>68958291.4123842</v>
+        <v>156.2487096695697</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>55235.43064517232</v>
+        <v>156.2487096695697</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>55235.43064517232</v>
+        <v>156.2487096695697</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>16976107.65504603</v>
+        <v>25001777.83428108</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>58036.29526205341</v>
+        <v>79793.38230758593</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>58036.29526205341</v>
+        <v>79793.38230758593</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-2800.864616881092</v>
+        <v>-79637.13359791636</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1745,17 +1749,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1764,40 +1768,40 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1000397.093686292</v>
+        <v>6027300.885906675</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1003527.316199909</v>
+        <v>74985592.29829088</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3130.222513617699</v>
+        <v>68958291.4123842</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3130.222513617699</v>
+        <v>55235.43064517232</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3130.222513617699</v>
+        <v>55235.43064517232</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1000397.093686292</v>
+        <v>16976107.65504603</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3420.062024124828</v>
+        <v>54179.38904954577</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3420.062024124828</v>
+        <v>54179.38904954577</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-289.8395105071294</v>
+        <v>1056.04159562655</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1810,12 +1814,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E41</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1825,44 +1829,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>1000397.093686292</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1000000</v>
+        <v>1003527.316199909</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>999999</v>
+        <v>3130.222513617699</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>3130.222513617699</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>3130.222513617699</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>1000000</v>
+        <v>1000397.093686292</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3418.704478161254</v>
+        <v>3192.775661195435</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3418.704478161254</v>
+        <v>3192.775661195435</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-3418.704478161254</v>
+        <v>-62.55314757773592</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1875,12 +1879,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1894,13 +1898,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>999999</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1915,19 +1919,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>654384.2290322618</v>
+        <v>1000000</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>2237.146294230693</v>
+        <v>3191.5083333865</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2237.146294230693</v>
+        <v>3191.5083333865</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-2237.146294230693</v>
+        <v>-3191.5083333865</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1940,12 +1944,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1959,13 +1963,13 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7547666.106224</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-7547666.106224</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -1980,19 +1984,19 @@
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>137651.9570648836</v>
+        <v>654384.2290322618</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>470.591362045378</v>
+        <v>2088.472720193163</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>470.591362045378</v>
+        <v>2088.472720193163</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-470.591362045378</v>
+        <v>-2088.472720193163</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2005,12 +2009,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2024,13 +2028,13 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>10068.978846</v>
+        <v>7547666.106224</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>-7547666.106224</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
@@ -2045,19 +2049,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>10068.978846</v>
+        <v>137651.9570648836</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>34.42286307133113</v>
+        <v>439.3173680795366</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>34.42286307133113</v>
+        <v>439.3173680795366</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-34.42286307133113</v>
+        <v>-439.3173680795366</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2070,12 +2074,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2085,44 +2089,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>10068.978846</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.369358080066628</v>
+        <v>10068.978846</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.000786013707660852</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>10068.978846</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.001260038973786547</v>
+        <v>32.13522989570139</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.001260038973786547</v>
+        <v>32.13522989570139</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-0.0004740252661256955</v>
+        <v>-32.13522989570139</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2135,12 +2139,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2154,40 +2158,40 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.369358080066628</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0</v>
+        <v>0.000786013707660852</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3.418704478161253e-09</v>
+        <v>0.001176300821238126</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3.418704478161253e-09</v>
+        <v>0.001176300821238126</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>-3.418704478161253e-09</v>
+        <v>-0.0003902871135772735</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2200,12 +2204,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2215,14 +2219,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -2240,19 +2244,19 @@
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0</v>
+        <v>3.1915083333865e-09</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0</v>
+        <v>3.1915083333865e-09</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>-3.1915083333865e-09</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
@@ -2265,12 +2269,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -2330,12 +2334,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -2395,12 +2399,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2460,12 +2464,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2503,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2520,21 +2524,17 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>0</v>
@@ -2589,17 +2589,21 @@
       <c r="R28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2659,12 +2663,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -2724,17 +2728,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2789,17 +2793,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2854,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E40</t>
+          <t>E38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDS raw (Diamond PAU ALM idle)</t>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2915,6 +2919,132 @@
         <v>0</v>
       </c>
       <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PSM_CURVE_DEDUCT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2993,11 +3123,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
+          <t>Base rate (BR_apr = apy_to_apr(SSR,12) + spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.03852302248128459</v>
+        <v>0.03785434185210828</v>
       </c>
     </row>
     <row r="9">
@@ -3017,7 +3147,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.03806862645474302</v>
+        <v>0.0378349784319679</v>
       </c>
     </row>
     <row r="11">
@@ -3027,7 +3157,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03804017286855644</v>
+        <v>0.03778801807182143</v>
       </c>
     </row>
     <row r="12">
@@ -3037,7 +3167,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-4.828496127281479</v>
+        <v>-0.6632378028684762</v>
       </c>
     </row>
     <row r="13">
@@ -3047,7 +3177,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>41099.72297488574</v>
+        <v>5860.38171770375</v>
       </c>
     </row>
     <row r="15">
@@ -3057,7 +3187,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3340116.861192898</v>
+        <v>3344816.775617297</v>
       </c>
     </row>
     <row r="16">
@@ -3067,7 +3197,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
     </row>
     <row r="17">
@@ -3077,7 +3207,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>41099.72297488574</v>
+        <v>5860.38171770375</v>
       </c>
     </row>
     <row r="19">
@@ -3107,7 +3237,7 @@
         <v>989284692.443311</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3138758.209130579</v>
+        <v>3178476.362042166</v>
       </c>
     </row>
     <row r="21">
@@ -3120,7 +3250,7 @@
         <v>51085267.06812943</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>160258.9290874331</v>
+        <v>160480.0318574274</v>
       </c>
     </row>
     <row r="23">
@@ -3142,7 +3272,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
     </row>
     <row r="25">
@@ -3162,7 +3292,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8003550.333979755</v>
+        <v>8043489.589661337</v>
       </c>
     </row>
     <row r="28">
@@ -3179,7 +3309,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8343733.524121915</v>
+        <v>8391061.35725352</v>
       </c>
     </row>
     <row r="31">
@@ -3189,7 +3319,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
     </row>
     <row r="32">
@@ -3199,7 +3329,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-5044716.385903903</v>
+        <v>-5052104.963353925</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -3297,14 +3427,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
+          <t>subsidised_apr = ref_rate + (base_apr − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apr</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
+          <t>Base rate composition: base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). Daily charge = utilized_d x base_apr / 365 — no intra-month compounding.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3698,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). sub_apr applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apr.</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3749,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>base APY</t>
+          <t>base APR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3629,12 +3759,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ref_rate APY</t>
+          <t>ref_rate APR</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>sub APY</t>
+          <t>sub APR</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3679,7 +3809,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -3688,13 +3818,13 @@
         <v>0.0385</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>111191.5088348251</v>
+        <v>112554.2899709449</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>275913.3721527929</v>
+        <v>277510.7730726121</v>
       </c>
     </row>
     <row r="7">
@@ -3728,7 +3858,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -3737,13 +3867,13 @@
         <v>0.0382</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>108898.3550035193</v>
+        <v>110401.6876642937</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>273638.1332155022</v>
+        <v>275376.1111768592</v>
       </c>
     </row>
     <row r="8">
@@ -3777,7 +3907,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -3786,13 +3916,13 @@
         <v>0.0382</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106968.9560583968</v>
+        <v>108469.5406008944</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>271746.5044682039</v>
+        <v>273481.7881088522</v>
       </c>
     </row>
     <row r="9">
@@ -3826,7 +3956,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -3835,13 +3965,13 @@
         <v>0.0382</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106968.9560583968</v>
+        <v>108469.5406008944</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>271746.5044682039</v>
+        <v>273481.7881088522</v>
       </c>
     </row>
     <row r="10">
@@ -3875,7 +4005,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
@@ -3884,13 +4014,13 @@
         <v>0.0382</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>106968.9560583968</v>
+        <v>108469.5406008944</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>271746.5044682039</v>
+        <v>273481.7881088522</v>
       </c>
     </row>
     <row r="11">
@@ -3924,7 +4054,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -3933,13 +4063,13 @@
         <v>0.0387</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>107404.0854824045</v>
+        <v>108365.2302084698</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>272210.3865265879</v>
+        <v>273406.2713043041</v>
       </c>
     </row>
     <row r="12">
@@ -3973,7 +4103,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
@@ -3982,13 +4112,13 @@
         <v>0.0386</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03872700106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>106666.2717059243</v>
+        <v>107824.4793196393</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>271487.0915123739</v>
+        <v>272880.05985738</v>
       </c>
     </row>
     <row r="13">
@@ -4022,7 +4152,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -4031,13 +4161,13 @@
         <v>0.0387</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>106323.7375890218</v>
+        <v>107283.3435333859</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>271159.4262068303</v>
+        <v>272353.8140607142</v>
       </c>
     </row>
     <row r="14">
@@ -4071,7 +4201,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
@@ -4080,13 +4210,13 @@
         <v>0.0383</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03850200106642065</v>
+        <v>0.03832982932837828</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102795.5691975566</v>
+        <v>104288.1586251961</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>267635.5479711227</v>
+        <v>269372.2848074792</v>
       </c>
     </row>
     <row r="15">
@@ -4120,7 +4250,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
@@ -4129,13 +4259,13 @@
         <v>0.0385</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102651.2147194106</v>
+        <v>103987.2869807801</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>267505.8001883973</v>
+        <v>269091.2258750811</v>
       </c>
     </row>
     <row r="16">
@@ -4169,7 +4299,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
@@ -4178,13 +4308,13 @@
         <v>0.0385</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>102623.3865606173</v>
+        <v>103959.0966204176</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>267477.6499235565</v>
+        <v>269063.0355147187</v>
       </c>
     </row>
     <row r="17">
@@ -4218,7 +4348,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -4227,13 +4357,13 @@
         <v>0.0385</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>102623.3865606173</v>
+        <v>103959.0966204176</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>267477.6499235565</v>
+        <v>269063.0355147187</v>
       </c>
     </row>
     <row r="18">
@@ -4267,7 +4397,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -4276,13 +4406,13 @@
         <v>0.0389</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03895200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>104040.4549164667</v>
+        <v>104598.0392544324</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>268952.155965133</v>
+        <v>269747.21513811</v>
       </c>
     </row>
     <row r="19">
@@ -4316,7 +4446,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -4325,13 +4455,13 @@
         <v>0.0384</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03857700106642065</v>
+        <v>0.03840482932837828</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>103253.1738200246</v>
+        <v>104757.1184668747</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>268173.2026978729</v>
+        <v>269918.0282004813</v>
       </c>
     </row>
     <row r="20">
@@ -4365,7 +4495,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
@@ -4374,13 +4504,13 @@
         <v>0.0383</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03850200106642065</v>
+        <v>0.03832982932837828</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>103661.8402686657</v>
+        <v>105165.0229485877</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>268605.9801092641</v>
+        <v>270344.0991700185</v>
       </c>
     </row>
     <row r="21">
@@ -4414,7 +4544,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -4423,13 +4553,13 @@
         <v>0.0384</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03857700106642065</v>
+        <v>0.03840482932837828</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>103843.9828058857</v>
+        <v>105354.7477821624</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>268803.8548569624</v>
+        <v>270549.5786220733</v>
       </c>
     </row>
     <row r="22">
@@ -4463,7 +4593,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
@@ -4472,13 +4602,13 @@
         <v>0.0385</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>104026.4041282723</v>
+        <v>105378.9797259008</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>269001.7527446232</v>
+        <v>270589.3091749623</v>
       </c>
     </row>
     <row r="23">
@@ -4512,7 +4642,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K23" t="n">
         <v>6</v>
@@ -4521,13 +4651,13 @@
         <v>0.0385</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>104026.4041282723</v>
+        <v>105378.9797259008</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>269001.7527446232</v>
+        <v>270589.3091749623</v>
       </c>
     </row>
     <row r="24">
@@ -4561,7 +4691,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -4570,13 +4700,13 @@
         <v>0.0385</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>104026.4041282723</v>
+        <v>105378.9797259008</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>269001.7527446232</v>
+        <v>270589.3091749623</v>
       </c>
     </row>
     <row r="25">
@@ -4610,7 +4740,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
@@ -4619,13 +4749,13 @@
         <v>0.0386</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03872700106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>94954.66485918801</v>
+        <v>96007.75423308634</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>259888.3859100873</v>
+        <v>261264.8337656769</v>
       </c>
     </row>
     <row r="26">
@@ -4659,7 +4789,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -4668,13 +4798,13 @@
         <v>0.0387</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>92478.20455894344</v>
+        <v>93326.47747610671</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>257423.9810488564</v>
+        <v>258598.804971717</v>
       </c>
     </row>
     <row r="27">
@@ -4708,7 +4838,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
@@ -4717,13 +4847,13 @@
         <v>0.0389</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.03895200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>97788.26030361245</v>
+        <v>98312.33723528276</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>262812.2652547772</v>
+        <v>263598.5791416011</v>
       </c>
     </row>
     <row r="28">
@@ -4757,7 +4887,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -4766,13 +4896,13 @@
         <v>0.0364</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>97488.36886466737</v>
+        <v>98833.56594140848</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>254917.6466288517</v>
+        <v>256491.2716441697</v>
       </c>
     </row>
     <row r="29">
@@ -4806,7 +4936,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -4815,13 +4945,13 @@
         <v>0.0364</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>102223.6502804317</v>
+        <v>103588.3234499376</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>259679.9420134012</v>
+        <v>261260.0839215551</v>
       </c>
     </row>
     <row r="30">
@@ -4855,7 +4985,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K30" t="n">
         <v>6</v>
@@ -4864,13 +4994,13 @@
         <v>0.0364</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>107386.9810657853</v>
+        <v>108758.7199191029</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>264843.2727987547</v>
+        <v>266430.4803907204</v>
       </c>
     </row>
     <row r="31">
@@ -4904,7 +5034,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K31" t="n">
         <v>6</v>
@@ -4913,13 +5043,13 @@
         <v>0.0364</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>112951.347251943</v>
+        <v>114330.7005800479</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>270407.6389849125</v>
+        <v>272002.4610516654</v>
       </c>
     </row>
     <row r="32">
@@ -4953,7 +5083,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K32" t="n">
         <v>6</v>
@@ -4962,13 +5092,13 @@
         <v>0.0364</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>114810.6536144164</v>
+        <v>116192.5512828731</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>272312.5571387323</v>
+        <v>273909.9859626196</v>
       </c>
     </row>
     <row r="33">
@@ -5002,7 +5132,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
@@ -5011,13 +5141,13 @@
         <v>0.0365</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>116899.3118077553</v>
+        <v>118291.0423997844</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>274415.7087448719</v>
+        <v>276022.9903256285</v>
       </c>
     </row>
     <row r="34">
@@ -5051,7 +5181,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K34" t="n">
         <v>6</v>
@@ -5060,13 +5190,13 @@
         <v>0.0365</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>120980.1423067609</v>
+        <v>122377.4572510606</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>278516.2945198623</v>
+        <v>280129.1874867055</v>
       </c>
     </row>
     <row r="35">
@@ -5100,7 +5230,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -5109,13 +5239,13 @@
         <v>0.0365</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>120954.9509923804</v>
+        <v>122352.2314639977</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>278516.2945198623</v>
+        <v>280129.1874867055</v>
       </c>
     </row>
     <row r="36">
@@ -5149,7 +5279,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K36" t="n">
         <v>6</v>
@@ -5158,13 +5288,13 @@
         <v>0.0366</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.03676759962619772</v>
+        <v>0.03661113937497726</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>121137.554287181</v>
+        <v>122542.0736909167</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>278714.5136705112</v>
+        <v>280334.6669387603</v>
       </c>
     </row>
     <row r="38">
@@ -5186,10 +5316,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3299017.138218012</v>
+        <v>3338956.393899593</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>8343733.524121915</v>
+        <v>8391061.35725352</v>
       </c>
     </row>
   </sheetData>
